--- a/artfynd/A 51597-2024 artfynd.xlsx
+++ b/artfynd/A 51597-2024 artfynd.xlsx
@@ -1018,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121153601</v>
+        <v>121153538</v>
       </c>
       <c r="B5" t="n">
-        <v>57501</v>
+        <v>90707</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,46 +1034,45 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 51590, Hafvet, Sm</t>
+          <t>A 51590, Afvet, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571000</v>
+        <v>570944</v>
       </c>
       <c r="R5" t="n">
-        <v>6421508</v>
+        <v>6421456</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1114,6 +1113,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1132,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121153538</v>
+        <v>121153601</v>
       </c>
       <c r="B6" t="n">
-        <v>90707</v>
+        <v>57501</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1148,45 +1148,46 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 51590, Afvet, Sm</t>
+          <t>A 51590, Hafvet, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>570944</v>
+        <v>571000</v>
       </c>
       <c r="R6" t="n">
-        <v>6421456</v>
+        <v>6421508</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1227,7 +1228,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 51597-2024 artfynd.xlsx
+++ b/artfynd/A 51597-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121119513</v>
       </c>
       <c r="B2" t="n">
-        <v>57501</v>
+        <v>57504</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>121119566</v>
       </c>
       <c r="B3" t="n">
-        <v>57364</v>
+        <v>57367</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121153492</v>
+        <v>121153538</v>
       </c>
       <c r="B4" t="n">
-        <v>98071</v>
+        <v>90717</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,50 +915,49 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 51590, Hafvet, Sm</t>
+          <t>A 51590, Afvet, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570926</v>
+        <v>570944</v>
       </c>
       <c r="R4" t="n">
-        <v>6421438</v>
+        <v>6421456</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1018,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121153538</v>
+        <v>121153601</v>
       </c>
       <c r="B5" t="n">
-        <v>90707</v>
+        <v>57504</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,45 +1033,46 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 51590, Afvet, Sm</t>
+          <t>A 51590, Hafvet, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570944</v>
+        <v>571000</v>
       </c>
       <c r="R5" t="n">
-        <v>6421456</v>
+        <v>6421508</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1113,7 +1113,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1132,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121153601</v>
+        <v>121153492</v>
       </c>
       <c r="B6" t="n">
-        <v>57501</v>
+        <v>98081</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,39 +1143,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1184,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571000</v>
+        <v>570926</v>
       </c>
       <c r="R6" t="n">
-        <v>6421508</v>
+        <v>6421438</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1228,6 +1227,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 51597-2024 artfynd.xlsx
+++ b/artfynd/A 51597-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1244,6 +1244,699 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121440654</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57504</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>A 51590, Hafvet, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>570916</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6421490</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>121440865</v>
+      </c>
+      <c r="B8" t="n">
+        <v>90697</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>A 51590, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>570913</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6421456</v>
+      </c>
+      <c r="S8" t="n">
+        <v>50</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Stefan Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>121440669</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57504</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>A 51590, Hafvet, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>570949</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6421533</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>121440675</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57367</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>A 51590, Hafvet, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>570949</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6421533</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>121440608</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91973</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>A 51590, Hafvet, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>570911</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6421570</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>121441081</v>
+      </c>
+      <c r="B12" t="n">
+        <v>97035</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>A 51590, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>571059</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6421539</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Stefan Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 51597-2024 artfynd.xlsx
+++ b/artfynd/A 51597-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121119513</v>
+        <v>121119566</v>
       </c>
       <c r="B2" t="n">
-        <v>57504</v>
+        <v>57367</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,33 +691,33 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -727,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570894</v>
+        <v>570933</v>
       </c>
       <c r="R2" t="n">
-        <v>6421594</v>
+        <v>6421545</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121119566</v>
+        <v>121119513</v>
       </c>
       <c r="B3" t="n">
-        <v>57367</v>
+        <v>57504</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,33 +805,33 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -841,13 +841,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570933</v>
+        <v>570894</v>
       </c>
       <c r="R3" t="n">
-        <v>6421545</v>
+        <v>6421594</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121153538</v>
+        <v>121153601</v>
       </c>
       <c r="B4" t="n">
-        <v>90717</v>
+        <v>57504</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,45 +919,46 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 51590, Afvet, Sm</t>
+          <t>A 51590, Hafvet, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570944</v>
+        <v>571000</v>
       </c>
       <c r="R4" t="n">
-        <v>6421456</v>
+        <v>6421508</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,7 +999,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1017,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121153601</v>
+        <v>121153538</v>
       </c>
       <c r="B5" t="n">
-        <v>57504</v>
+        <v>90717</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,46 +1033,45 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 51590, Hafvet, Sm</t>
+          <t>A 51590, Afvet, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571000</v>
+        <v>570944</v>
       </c>
       <c r="R5" t="n">
-        <v>6421508</v>
+        <v>6421456</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1113,6 +1112,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1246,10 +1246,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121440654</v>
+        <v>121440608</v>
       </c>
       <c r="B7" t="n">
-        <v>57504</v>
+        <v>91973</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1258,39 +1258,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1298,13 +1297,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>570916</v>
+        <v>570911</v>
       </c>
       <c r="R7" t="n">
-        <v>6421490</v>
+        <v>6421570</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1342,6 +1341,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1490,10 +1490,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121440669</v>
+        <v>121440675</v>
       </c>
       <c r="B9" t="n">
-        <v>57504</v>
+        <v>57367</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1506,21 +1506,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1532,7 +1532,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1604,10 +1604,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121440675</v>
+        <v>121441081</v>
       </c>
       <c r="B10" t="n">
-        <v>57367</v>
+        <v>97035</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1616,53 +1616,45 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>A 51590, Hafvet, Sm</t>
+          <t>A 51590, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>570949</v>
+        <v>571059</v>
       </c>
       <c r="R10" t="n">
-        <v>6421533</v>
+        <v>6421539</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1700,28 +1692,29 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121440608</v>
+        <v>121440669</v>
       </c>
       <c r="B11" t="n">
-        <v>91973</v>
+        <v>57504</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1730,38 +1723,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1769,13 +1763,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>570911</v>
+        <v>570949</v>
       </c>
       <c r="R11" t="n">
-        <v>6421570</v>
+        <v>6421533</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1813,7 +1807,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1832,10 +1825,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121441081</v>
+        <v>121440654</v>
       </c>
       <c r="B12" t="n">
-        <v>97035</v>
+        <v>57504</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1844,45 +1837,53 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>A 51590, Sm</t>
+          <t>A 51590, Hafvet, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>571059</v>
+        <v>570916</v>
       </c>
       <c r="R12" t="n">
-        <v>6421539</v>
+        <v>6421490</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1920,19 +1921,18 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 51597-2024 artfynd.xlsx
+++ b/artfynd/A 51597-2024 artfynd.xlsx
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121153601</v>
+        <v>121153538</v>
       </c>
       <c r="B4" t="n">
-        <v>57504</v>
+        <v>90729</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,46 +919,45 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 51590, Hafvet, Sm</t>
+          <t>A 51590, Afvet, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571000</v>
+        <v>570944</v>
       </c>
       <c r="R4" t="n">
-        <v>6421508</v>
+        <v>6421456</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,6 +998,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1017,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121153538</v>
+        <v>121153601</v>
       </c>
       <c r="B5" t="n">
-        <v>90717</v>
+        <v>57504</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,45 +1033,46 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 51590, Afvet, Sm</t>
+          <t>A 51590, Hafvet, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570944</v>
+        <v>571000</v>
       </c>
       <c r="R5" t="n">
-        <v>6421456</v>
+        <v>6421508</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1112,7 +1113,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1134,7 +1134,7 @@
         <v>121153492</v>
       </c>
       <c r="B6" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1246,10 +1246,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121440608</v>
+        <v>121440865</v>
       </c>
       <c r="B7" t="n">
-        <v>91973</v>
+        <v>90709</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1258,32 +1258,28 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -1293,17 +1289,17 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 51590, Hafvet, Sm</t>
+          <t>A 51590, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>570911</v>
+        <v>570913</v>
       </c>
       <c r="R7" t="n">
-        <v>6421570</v>
+        <v>6421456</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1333,6 +1329,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1345,25 +1346,40 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121440865</v>
+        <v>121440675</v>
       </c>
       <c r="B8" t="n">
-        <v>90697</v>
+        <v>57367</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1376,44 +1392,49 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A 51590, Sm</t>
+          <t>A 51590, Hafvet, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>570913</v>
+        <v>570949</v>
       </c>
       <c r="R8" t="n">
-        <v>6421456</v>
+        <v>6421533</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1445,55 +1466,34 @@
           <t>2024-12-02</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121440675</v>
+        <v>121441081</v>
       </c>
       <c r="B9" t="n">
-        <v>57367</v>
+        <v>97048</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1502,53 +1502,45 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 51590, Hafvet, Sm</t>
+          <t>A 51590, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>570949</v>
+        <v>571059</v>
       </c>
       <c r="R9" t="n">
-        <v>6421533</v>
+        <v>6421539</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1586,28 +1578,29 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121441081</v>
+        <v>121440654</v>
       </c>
       <c r="B10" t="n">
-        <v>97035</v>
+        <v>57504</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1616,45 +1609,53 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>A 51590, Sm</t>
+          <t>A 51590, Hafvet, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>571059</v>
+        <v>570916</v>
       </c>
       <c r="R10" t="n">
-        <v>6421539</v>
+        <v>6421490</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1692,29 +1693,28 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121440669</v>
+        <v>121440608</v>
       </c>
       <c r="B11" t="n">
-        <v>57504</v>
+        <v>91985</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1723,39 +1723,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1763,13 +1762,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>570949</v>
+        <v>570911</v>
       </c>
       <c r="R11" t="n">
-        <v>6421533</v>
+        <v>6421570</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1807,6 +1806,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1825,7 +1825,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121440654</v>
+        <v>121440669</v>
       </c>
       <c r="B12" t="n">
         <v>57504</v>
@@ -1877,10 +1877,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>570916</v>
+        <v>570949</v>
       </c>
       <c r="R12" t="n">
-        <v>6421490</v>
+        <v>6421533</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>

--- a/artfynd/A 51597-2024 artfynd.xlsx
+++ b/artfynd/A 51597-2024 artfynd.xlsx
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121153538</v>
+        <v>121153601</v>
       </c>
       <c r="B4" t="n">
-        <v>90729</v>
+        <v>57504</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,45 +919,46 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 51590, Afvet, Sm</t>
+          <t>A 51590, Hafvet, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570944</v>
+        <v>571000</v>
       </c>
       <c r="R4" t="n">
-        <v>6421456</v>
+        <v>6421508</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,7 +999,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1017,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121153601</v>
+        <v>121153538</v>
       </c>
       <c r="B5" t="n">
-        <v>57504</v>
+        <v>90730</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,46 +1033,45 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 51590, Hafvet, Sm</t>
+          <t>A 51590, Afvet, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571000</v>
+        <v>570944</v>
       </c>
       <c r="R5" t="n">
-        <v>6421508</v>
+        <v>6421456</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1113,6 +1112,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1134,7 +1134,7 @@
         <v>121153492</v>
       </c>
       <c r="B6" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>121440865</v>
       </c>
       <c r="B7" t="n">
-        <v>90709</v>
+        <v>90710</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1376,10 +1376,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121440675</v>
+        <v>121440608</v>
       </c>
       <c r="B8" t="n">
-        <v>57367</v>
+        <v>91986</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1388,39 +1388,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1428,13 +1427,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>570949</v>
+        <v>570911</v>
       </c>
       <c r="R8" t="n">
-        <v>6421533</v>
+        <v>6421570</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1472,6 +1471,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1490,10 +1490,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121441081</v>
+        <v>121440669</v>
       </c>
       <c r="B9" t="n">
-        <v>97048</v>
+        <v>57504</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1502,45 +1502,53 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 51590, Sm</t>
+          <t>A 51590, Hafvet, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>571059</v>
+        <v>570949</v>
       </c>
       <c r="R9" t="n">
-        <v>6421539</v>
+        <v>6421533</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1578,29 +1586,28 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121440654</v>
+        <v>121440675</v>
       </c>
       <c r="B10" t="n">
-        <v>57504</v>
+        <v>57367</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1613,21 +1620,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1639,7 +1646,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1649,10 +1656,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>570916</v>
+        <v>570949</v>
       </c>
       <c r="R10" t="n">
-        <v>6421490</v>
+        <v>6421533</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1711,10 +1718,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121440608</v>
+        <v>121440654</v>
       </c>
       <c r="B11" t="n">
-        <v>91985</v>
+        <v>57504</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1723,38 +1730,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1762,13 +1770,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>570911</v>
+        <v>570916</v>
       </c>
       <c r="R11" t="n">
-        <v>6421570</v>
+        <v>6421490</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1806,7 +1814,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1825,10 +1832,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121440669</v>
+        <v>121441081</v>
       </c>
       <c r="B12" t="n">
-        <v>57504</v>
+        <v>97049</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1837,53 +1844,45 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>A 51590, Hafvet, Sm</t>
+          <t>A 51590, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>570949</v>
+        <v>571059</v>
       </c>
       <c r="R12" t="n">
-        <v>6421533</v>
+        <v>6421539</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1921,18 +1920,19 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 51597-2024 artfynd.xlsx
+++ b/artfynd/A 51597-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121119566</v>
+        <v>121119513</v>
       </c>
       <c r="B2" t="n">
-        <v>57367</v>
+        <v>57507</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,33 +691,33 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -727,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570933</v>
+        <v>570894</v>
       </c>
       <c r="R2" t="n">
-        <v>6421545</v>
+        <v>6421594</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121119513</v>
+        <v>121119566</v>
       </c>
       <c r="B3" t="n">
-        <v>57504</v>
+        <v>57370</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,33 +805,33 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -841,13 +841,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570894</v>
+        <v>570933</v>
       </c>
       <c r="R3" t="n">
-        <v>6421594</v>
+        <v>6421545</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>121153601</v>
       </c>
       <c r="B4" t="n">
-        <v>57504</v>
+        <v>57507</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1017,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121153538</v>
+        <v>121153492</v>
       </c>
       <c r="B5" t="n">
-        <v>90730</v>
+        <v>98098</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,49 +1029,50 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 51590, Afvet, Sm</t>
+          <t>A 51590, Hafvet, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570944</v>
+        <v>570926</v>
       </c>
       <c r="R5" t="n">
-        <v>6421456</v>
+        <v>6421438</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1131,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121153492</v>
+        <v>121153538</v>
       </c>
       <c r="B6" t="n">
-        <v>98095</v>
+        <v>90733</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,50 +1144,49 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 51590, Hafvet, Sm</t>
+          <t>A 51590, Afvet, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>570926</v>
+        <v>570944</v>
       </c>
       <c r="R6" t="n">
-        <v>6421438</v>
+        <v>6421456</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1246,10 +1246,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121440865</v>
+        <v>121440675</v>
       </c>
       <c r="B7" t="n">
-        <v>90710</v>
+        <v>57370</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1262,44 +1262,49 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 51590, Sm</t>
+          <t>A 51590, Hafvet, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>570913</v>
+        <v>570949</v>
       </c>
       <c r="R7" t="n">
-        <v>6421456</v>
+        <v>6421533</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1331,55 +1336,34 @@
           <t>2024-12-02</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121440608</v>
+        <v>121440654</v>
       </c>
       <c r="B8" t="n">
-        <v>91986</v>
+        <v>57507</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1388,38 +1372,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1427,13 +1412,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>570911</v>
+        <v>570916</v>
       </c>
       <c r="R8" t="n">
-        <v>6421570</v>
+        <v>6421490</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1471,7 +1456,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1490,10 +1474,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121440669</v>
+        <v>121441081</v>
       </c>
       <c r="B9" t="n">
-        <v>57504</v>
+        <v>97052</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1502,53 +1486,45 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 51590, Hafvet, Sm</t>
+          <t>A 51590, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>570949</v>
+        <v>571059</v>
       </c>
       <c r="R9" t="n">
-        <v>6421533</v>
+        <v>6421539</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1586,28 +1562,29 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121440675</v>
+        <v>121440865</v>
       </c>
       <c r="B10" t="n">
-        <v>57367</v>
+        <v>90713</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1620,49 +1597,44 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>A 51590, Hafvet, Sm</t>
+          <t>A 51590, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>570949</v>
+        <v>570913</v>
       </c>
       <c r="R10" t="n">
-        <v>6421533</v>
+        <v>6421456</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1694,34 +1666,55 @@
           <t>2024-12-02</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121440654</v>
+        <v>121440608</v>
       </c>
       <c r="B11" t="n">
-        <v>57504</v>
+        <v>91989</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1730,39 +1723,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1770,13 +1762,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>570916</v>
+        <v>570911</v>
       </c>
       <c r="R11" t="n">
-        <v>6421490</v>
+        <v>6421570</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1814,6 +1806,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1832,10 +1825,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121441081</v>
+        <v>121440669</v>
       </c>
       <c r="B12" t="n">
-        <v>97049</v>
+        <v>57507</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1844,45 +1837,53 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>A 51590, Sm</t>
+          <t>A 51590, Hafvet, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>571059</v>
+        <v>570949</v>
       </c>
       <c r="R12" t="n">
-        <v>6421539</v>
+        <v>6421533</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1920,19 +1921,18 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 51597-2024 artfynd.xlsx
+++ b/artfynd/A 51597-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121119513</v>
+        <v>121119566</v>
       </c>
       <c r="B2" t="n">
-        <v>57507</v>
+        <v>57370</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,33 +691,33 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -727,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570894</v>
+        <v>570933</v>
       </c>
       <c r="R2" t="n">
-        <v>6421594</v>
+        <v>6421545</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121119566</v>
+        <v>121119513</v>
       </c>
       <c r="B3" t="n">
-        <v>57370</v>
+        <v>57507</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,33 +805,33 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -841,13 +841,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570933</v>
+        <v>570894</v>
       </c>
       <c r="R3" t="n">
-        <v>6421545</v>
+        <v>6421594</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -1246,10 +1246,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121440675</v>
+        <v>121440608</v>
       </c>
       <c r="B7" t="n">
-        <v>57370</v>
+        <v>91989</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1258,39 +1258,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1298,13 +1297,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>570949</v>
+        <v>570911</v>
       </c>
       <c r="R7" t="n">
-        <v>6421533</v>
+        <v>6421570</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1342,6 +1341,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1711,10 +1711,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121440608</v>
+        <v>121440669</v>
       </c>
       <c r="B11" t="n">
-        <v>91989</v>
+        <v>57507</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1723,38 +1723,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1762,13 +1763,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>570911</v>
+        <v>570949</v>
       </c>
       <c r="R11" t="n">
-        <v>6421570</v>
+        <v>6421533</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1806,7 +1807,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1825,10 +1825,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121440669</v>
+        <v>121440675</v>
       </c>
       <c r="B12" t="n">
-        <v>57507</v>
+        <v>57370</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1841,21 +1841,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1867,7 +1867,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>

--- a/artfynd/A 51597-2024 artfynd.xlsx
+++ b/artfynd/A 51597-2024 artfynd.xlsx
@@ -1246,10 +1246,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121440608</v>
+        <v>121440669</v>
       </c>
       <c r="B7" t="n">
-        <v>91989</v>
+        <v>57508</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1258,38 +1258,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1297,13 +1298,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>570911</v>
+        <v>570949</v>
       </c>
       <c r="R7" t="n">
-        <v>6421570</v>
+        <v>6421533</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1341,7 +1342,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1360,10 +1360,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121440654</v>
+        <v>121440675</v>
       </c>
       <c r="B8" t="n">
-        <v>57507</v>
+        <v>57371</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1376,21 +1376,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1402,7 +1402,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1412,10 +1412,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>570916</v>
+        <v>570949</v>
       </c>
       <c r="R8" t="n">
-        <v>6421490</v>
+        <v>6421533</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1474,10 +1474,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121441081</v>
+        <v>121440654</v>
       </c>
       <c r="B9" t="n">
-        <v>97052</v>
+        <v>57508</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1486,45 +1486,53 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 51590, Sm</t>
+          <t>A 51590, Hafvet, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>571059</v>
+        <v>570916</v>
       </c>
       <c r="R9" t="n">
-        <v>6421539</v>
+        <v>6421490</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1562,19 +1570,18 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1584,7 +1591,7 @@
         <v>121440865</v>
       </c>
       <c r="B10" t="n">
-        <v>90713</v>
+        <v>90719</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1711,10 +1718,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121440669</v>
+        <v>121440608</v>
       </c>
       <c r="B11" t="n">
-        <v>57507</v>
+        <v>91995</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1723,39 +1730,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1763,13 +1769,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>570949</v>
+        <v>570911</v>
       </c>
       <c r="R11" t="n">
-        <v>6421533</v>
+        <v>6421570</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1807,6 +1813,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1825,10 +1832,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121440675</v>
+        <v>121441081</v>
       </c>
       <c r="B12" t="n">
-        <v>57370</v>
+        <v>97058</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1837,53 +1844,45 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>A 51590, Hafvet, Sm</t>
+          <t>A 51590, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>570949</v>
+        <v>571059</v>
       </c>
       <c r="R12" t="n">
-        <v>6421533</v>
+        <v>6421539</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1921,18 +1920,19 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 51597-2024 artfynd.xlsx
+++ b/artfynd/A 51597-2024 artfynd.xlsx
@@ -1249,7 +1249,7 @@
         <v>121440669</v>
       </c>
       <c r="B7" t="n">
-        <v>57508</v>
+        <v>57509</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1360,10 +1360,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121440675</v>
+        <v>121441081</v>
       </c>
       <c r="B8" t="n">
-        <v>57371</v>
+        <v>97059</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1372,53 +1372,45 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A 51590, Hafvet, Sm</t>
+          <t>A 51590, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>570949</v>
+        <v>571059</v>
       </c>
       <c r="R8" t="n">
-        <v>6421533</v>
+        <v>6421539</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1456,28 +1448,29 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121440654</v>
+        <v>121440865</v>
       </c>
       <c r="B9" t="n">
-        <v>57508</v>
+        <v>90720</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1490,49 +1483,44 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 51590, Hafvet, Sm</t>
+          <t>A 51590, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>570916</v>
+        <v>570913</v>
       </c>
       <c r="R9" t="n">
-        <v>6421490</v>
+        <v>6421456</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1564,34 +1552,55 @@
           <t>2024-12-02</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121440865</v>
+        <v>121440675</v>
       </c>
       <c r="B10" t="n">
-        <v>90719</v>
+        <v>57372</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1604,44 +1613,49 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>A 51590, Sm</t>
+          <t>A 51590, Hafvet, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>570913</v>
+        <v>570949</v>
       </c>
       <c r="R10" t="n">
-        <v>6421456</v>
+        <v>6421533</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1673,55 +1687,34 @@
           <t>2024-12-02</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121440608</v>
+        <v>121440654</v>
       </c>
       <c r="B11" t="n">
-        <v>91995</v>
+        <v>57509</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1730,38 +1723,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1769,13 +1763,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>570911</v>
+        <v>570916</v>
       </c>
       <c r="R11" t="n">
-        <v>6421570</v>
+        <v>6421490</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1813,7 +1807,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1832,10 +1825,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121441081</v>
+        <v>121440608</v>
       </c>
       <c r="B12" t="n">
-        <v>97058</v>
+        <v>91996</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1848,41 +1841,48 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>A 51590, Sm</t>
+          <t>A 51590, Hafvet, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>571059</v>
+        <v>570911</v>
       </c>
       <c r="R12" t="n">
-        <v>6421539</v>
+        <v>6421570</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1927,12 +1927,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 51597-2024 artfynd.xlsx
+++ b/artfynd/A 51597-2024 artfynd.xlsx
@@ -1246,10 +1246,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121440669</v>
+        <v>121441081</v>
       </c>
       <c r="B7" t="n">
-        <v>57509</v>
+        <v>97059</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1258,53 +1258,45 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 51590, Hafvet, Sm</t>
+          <t>A 51590, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>570949</v>
+        <v>571059</v>
       </c>
       <c r="R7" t="n">
-        <v>6421533</v>
+        <v>6421539</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1342,28 +1334,29 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121441081</v>
+        <v>121440865</v>
       </c>
       <c r="B8" t="n">
-        <v>97059</v>
+        <v>90720</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1372,31 +1365,34 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1404,13 +1400,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>571059</v>
+        <v>570913</v>
       </c>
       <c r="R8" t="n">
-        <v>6421539</v>
+        <v>6421456</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1440,6 +1436,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1451,6 +1452,21 @@
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1467,10 +1483,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121440865</v>
+        <v>121440675</v>
       </c>
       <c r="B9" t="n">
-        <v>90720</v>
+        <v>57372</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1483,44 +1499,49 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 51590, Sm</t>
+          <t>A 51590, Hafvet, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>570913</v>
+        <v>570949</v>
       </c>
       <c r="R9" t="n">
-        <v>6421456</v>
+        <v>6421533</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1552,55 +1573,34 @@
           <t>2024-12-02</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121440675</v>
+        <v>121440669</v>
       </c>
       <c r="B10" t="n">
-        <v>57372</v>
+        <v>57509</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1613,21 +1613,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1639,7 +1639,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>

--- a/artfynd/A 51597-2024 artfynd.xlsx
+++ b/artfynd/A 51597-2024 artfynd.xlsx
@@ -1246,10 +1246,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121441081</v>
+        <v>121440675</v>
       </c>
       <c r="B7" t="n">
-        <v>97059</v>
+        <v>57372</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1258,45 +1258,53 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 51590, Sm</t>
+          <t>A 51590, Hafvet, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>571059</v>
+        <v>570949</v>
       </c>
       <c r="R7" t="n">
-        <v>6421539</v>
+        <v>6421533</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1334,29 +1342,28 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121440865</v>
+        <v>121440669</v>
       </c>
       <c r="B8" t="n">
-        <v>90720</v>
+        <v>57509</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1369,44 +1376,49 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A 51590, Sm</t>
+          <t>A 51590, Hafvet, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>570913</v>
+        <v>570949</v>
       </c>
       <c r="R8" t="n">
-        <v>6421456</v>
+        <v>6421533</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1438,55 +1450,34 @@
           <t>2024-12-02</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121440675</v>
+        <v>121441081</v>
       </c>
       <c r="B9" t="n">
-        <v>57372</v>
+        <v>97059</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1495,53 +1486,45 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 51590, Hafvet, Sm</t>
+          <t>A 51590, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>570949</v>
+        <v>571059</v>
       </c>
       <c r="R9" t="n">
-        <v>6421533</v>
+        <v>6421539</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1579,28 +1562,29 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121440669</v>
+        <v>121440865</v>
       </c>
       <c r="B10" t="n">
-        <v>57509</v>
+        <v>90720</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1613,49 +1597,44 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>A 51590, Hafvet, Sm</t>
+          <t>A 51590, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>570949</v>
+        <v>570913</v>
       </c>
       <c r="R10" t="n">
-        <v>6421533</v>
+        <v>6421456</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1687,24 +1666,45 @@
           <t>2024-12-02</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 51597-2024 artfynd.xlsx
+++ b/artfynd/A 51597-2024 artfynd.xlsx
@@ -1246,10 +1246,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121440675</v>
+        <v>121440608</v>
       </c>
       <c r="B7" t="n">
-        <v>57372</v>
+        <v>91996</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1258,39 +1258,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1298,13 +1297,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>570949</v>
+        <v>570911</v>
       </c>
       <c r="R7" t="n">
-        <v>6421533</v>
+        <v>6421570</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1342,6 +1341,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1474,10 +1474,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121441081</v>
+        <v>121440654</v>
       </c>
       <c r="B9" t="n">
-        <v>97059</v>
+        <v>57509</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1486,45 +1486,53 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 51590, Sm</t>
+          <t>A 51590, Hafvet, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>571059</v>
+        <v>570916</v>
       </c>
       <c r="R9" t="n">
-        <v>6421539</v>
+        <v>6421490</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1562,29 +1570,28 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121440865</v>
+        <v>121441081</v>
       </c>
       <c r="B10" t="n">
-        <v>90720</v>
+        <v>97059</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1593,34 +1600,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1628,13 +1632,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>570913</v>
+        <v>571059</v>
       </c>
       <c r="R10" t="n">
-        <v>6421456</v>
+        <v>6421539</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1664,11 +1668,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-12-02</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>granlåga</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1680,21 +1679,6 @@
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1711,10 +1695,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121440654</v>
+        <v>121440675</v>
       </c>
       <c r="B11" t="n">
-        <v>57509</v>
+        <v>57372</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1727,21 +1711,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1753,7 +1737,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1763,10 +1747,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>570916</v>
+        <v>570949</v>
       </c>
       <c r="R11" t="n">
-        <v>6421490</v>
+        <v>6421533</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1825,10 +1809,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121440608</v>
+        <v>121440865</v>
       </c>
       <c r="B12" t="n">
-        <v>91996</v>
+        <v>90720</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1837,32 +1821,28 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -1872,17 +1852,17 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>A 51590, Hafvet, Sm</t>
+          <t>A 51590, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>570911</v>
+        <v>570913</v>
       </c>
       <c r="R12" t="n">
-        <v>6421570</v>
+        <v>6421456</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1912,6 +1892,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1924,15 +1909,30 @@
       <c r="AG12" t="b">
         <v>0</v>
       </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 51597-2024 artfynd.xlsx
+++ b/artfynd/A 51597-2024 artfynd.xlsx
@@ -1246,10 +1246,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121440608</v>
+        <v>121440669</v>
       </c>
       <c r="B7" t="n">
-        <v>91996</v>
+        <v>57510</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1258,38 +1258,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1297,13 +1298,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>570911</v>
+        <v>570949</v>
       </c>
       <c r="R7" t="n">
-        <v>6421570</v>
+        <v>6421533</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1341,7 +1342,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1360,10 +1360,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121440669</v>
+        <v>121440865</v>
       </c>
       <c r="B8" t="n">
-        <v>57509</v>
+        <v>90728</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1376,49 +1376,44 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A 51590, Hafvet, Sm</t>
+          <t>A 51590, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>570949</v>
+        <v>570913</v>
       </c>
       <c r="R8" t="n">
-        <v>6421533</v>
+        <v>6421456</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1450,34 +1445,55 @@
           <t>2024-12-02</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121440654</v>
+        <v>121440608</v>
       </c>
       <c r="B9" t="n">
-        <v>57509</v>
+        <v>92004</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1486,39 +1502,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1526,13 +1541,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>570916</v>
+        <v>570911</v>
       </c>
       <c r="R9" t="n">
-        <v>6421490</v>
+        <v>6421570</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1570,6 +1585,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1591,7 +1607,7 @@
         <v>121441081</v>
       </c>
       <c r="B10" t="n">
-        <v>97059</v>
+        <v>97067</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1698,7 +1714,7 @@
         <v>121440675</v>
       </c>
       <c r="B11" t="n">
-        <v>57372</v>
+        <v>57373</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1809,10 +1825,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121440865</v>
+        <v>121440654</v>
       </c>
       <c r="B12" t="n">
-        <v>90720</v>
+        <v>57510</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1825,44 +1841,49 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>A 51590, Sm</t>
+          <t>A 51590, Hafvet, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>570913</v>
+        <v>570916</v>
       </c>
       <c r="R12" t="n">
-        <v>6421456</v>
+        <v>6421490</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1894,45 +1915,24 @@
           <t>2024-12-02</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 51597-2024 artfynd.xlsx
+++ b/artfynd/A 51597-2024 artfynd.xlsx
@@ -1246,10 +1246,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121440865</v>
+        <v>121440669</v>
       </c>
       <c r="B7" t="n">
-        <v>90728</v>
+        <v>57510</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1262,44 +1262,49 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 51590, Sm</t>
+          <t>A 51590, Hafvet, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>570913</v>
+        <v>570949</v>
       </c>
       <c r="R7" t="n">
-        <v>6421456</v>
+        <v>6421533</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1331,55 +1336,34 @@
           <t>2024-12-02</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121440654</v>
+        <v>121440865</v>
       </c>
       <c r="B8" t="n">
-        <v>57510</v>
+        <v>90728</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1392,49 +1376,44 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A 51590, Hafvet, Sm</t>
+          <t>A 51590, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>570916</v>
+        <v>570913</v>
       </c>
       <c r="R8" t="n">
-        <v>6421490</v>
+        <v>6421456</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1466,34 +1445,55 @@
           <t>2024-12-02</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121441081</v>
+        <v>121440608</v>
       </c>
       <c r="B9" t="n">
-        <v>97067</v>
+        <v>92004</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1506,41 +1506,48 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 51590, Sm</t>
+          <t>A 51590, Hafvet, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>571059</v>
+        <v>570911</v>
       </c>
       <c r="R9" t="n">
-        <v>6421539</v>
+        <v>6421570</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1585,22 +1592,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121440675</v>
+        <v>121440654</v>
       </c>
       <c r="B10" t="n">
-        <v>57373</v>
+        <v>57510</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1613,21 +1620,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1639,7 +1646,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1649,10 +1656,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>570949</v>
+        <v>570916</v>
       </c>
       <c r="R10" t="n">
-        <v>6421533</v>
+        <v>6421490</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1711,10 +1718,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121440608</v>
+        <v>121441081</v>
       </c>
       <c r="B11" t="n">
-        <v>92004</v>
+        <v>97067</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1727,48 +1734,41 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>A 51590, Hafvet, Sm</t>
+          <t>A 51590, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>570911</v>
+        <v>571059</v>
       </c>
       <c r="R11" t="n">
-        <v>6421570</v>
+        <v>6421539</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1813,22 +1813,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121440669</v>
+        <v>121440675</v>
       </c>
       <c r="B12" t="n">
-        <v>57510</v>
+        <v>57373</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1841,21 +1841,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1867,7 +1867,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
